--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -3943,7 +3943,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 10.5, "op_wape_pct": 36.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 204.6, "rev_act": 175.5, "op_pred": 11.58, "op_act": 9.26}, {"q": "2025Q4", "rev_pred": 183.54, "rev_act": 160.11, "op_pred": 10.39, "op_act": 14.58}, {"q": "2026Q1", "rev_pred": 204.6, "rev_act": 182.59, "op_pred": 11.58, "op_act": 16.02}, {"q": "2026Q2", "rev_pred": 225.66, "rev_act": 222.59, "op_pred": 12.77, "op_act": 26.07}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 10.5, "op_wape_pct": 36.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 204.6, "rev_act": 175.5, "op_pred": 11.58, "op_act": 9.26}, {"q": "2025Q4", "rev_pred": 183.54, "rev_act": 160.11, "op_pred": 10.39, "op_act": 14.58}, {"q": "2026Q1", "rev_pred": 204.6, "rev_act": 182.59, "op_pred": 11.58, "op_act": 16.02}, {"q": "2026Q2", "rev_pred": 225.66, "rev_act": 222.59, "op_pred": 12.77, "op_act": 26.07}]}</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AJ$1</definedName>
@@ -4004,7 +4004,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4791,35 +4791,35 @@
         <v>1418.75</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="Z6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE6" s="11" t="n"/>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
     </row>
@@ -4895,35 +4895,35 @@
         <v>1355.4</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Z7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="11" t="n"/>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
     </row>
@@ -4999,35 +4999,35 @@
         <v>890.41</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="Z8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE8" s="11" t="n"/>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
     </row>
@@ -5103,35 +5103,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Z9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="11" t="n"/>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>1631.97</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="Z10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE10" s="11" t="n"/>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
     </row>
@@ -5311,35 +5311,35 @@
         <v>1539.06</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Z11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="Z12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE12" s="11" t="n"/>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
     </row>
@@ -5519,35 +5519,35 @@
         <v>202.16</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Z13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="11" t="n"/>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
     </row>
@@ -5634,7 +5634,7 @@
         <v>12270</v>
       </c>
       <c r="Y15" s="20" t="n">
-        <v>11970</v>
+        <v>12300</v>
       </c>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="10" t="n"/>
@@ -5850,7 +5850,7 @@
         <v>8267.299999999999</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>11955</v>
+        <v>12070</v>
       </c>
       <c r="Z18" s="11" t="n"/>
       <c r="AA18" s="10" t="n"/>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>11970</v>
+        <v>12300</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.2201633165829146</v>
+        <v>0.2201633165829145</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0124207622757147</v>
+        <v>0.01242076227571334</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03707514890139745</v>
+        <v>0.0370751489013967</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25257,7 +25257,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>90.27</v>
+        <v>92.76000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -25267,7 +25267,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -4004,7 +4004,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4791,35 +4791,35 @@
         <v>1418.75</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="Z6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE6" s="11" t="n"/>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
     </row>
@@ -4895,35 +4895,35 @@
         <v>1355.4</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Z7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="11" t="n"/>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
     </row>
@@ -4999,35 +4999,35 @@
         <v>890.41</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="Z8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE8" s="11" t="n"/>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
     </row>
@@ -5103,35 +5103,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Z9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="11" t="n"/>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>1631.97</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="Z10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE10" s="11" t="n"/>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
     </row>
@@ -5311,35 +5311,35 @@
         <v>1539.06</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Z11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="Z12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE12" s="11" t="n"/>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
     </row>
@@ -5519,35 +5519,35 @@
         <v>202.16</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Z13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="11" t="n"/>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
     </row>
@@ -5634,7 +5634,7 @@
         <v>12270</v>
       </c>
       <c r="Y15" s="20" t="n">
-        <v>12300</v>
+        <v>13690</v>
       </c>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="10" t="n"/>
@@ -5706,7 +5706,7 @@
         <v>14140</v>
       </c>
       <c r="Y16" s="20" t="n">
-        <v>13300</v>
+        <v>14260</v>
       </c>
       <c r="Z16" s="11" t="n"/>
       <c r="AA16" s="10" t="n"/>
@@ -5850,7 +5850,7 @@
         <v>8267.299999999999</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>12070</v>
+        <v>12495</v>
       </c>
       <c r="Z18" s="11" t="n"/>
       <c r="AA18" s="10" t="n"/>
@@ -8193,11 +8193,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>12300</v>
+        <v>13690</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,900원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,980원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25257,7 +25257,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>92.76000000000001</v>
+        <v>103.24</v>
       </c>
     </row>
     <row r="32">
@@ -25267,7 +25267,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -4004,7 +4004,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -4791,35 +4791,35 @@
         <v>1418.75</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="Z6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE6" s="11" t="n"/>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
     </row>
@@ -4895,35 +4895,35 @@
         <v>1355.4</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Z7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="11" t="n"/>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
     </row>
@@ -4999,35 +4999,35 @@
         <v>890.41</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="Z8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE8" s="11" t="n"/>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
     </row>
@@ -5103,35 +5103,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Z9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="11" t="n"/>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>1631.97</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="Z10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE10" s="11" t="n"/>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
     </row>
@@ -5311,35 +5311,35 @@
         <v>1539.06</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Z11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
     </row>
@@ -5415,35 +5415,35 @@
         <v>210.43</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="Z12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE12" s="11" t="n"/>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
     </row>
@@ -5519,35 +5519,35 @@
         <v>202.16</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Z13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="11" t="n"/>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
     </row>
@@ -5634,7 +5634,7 @@
         <v>12270</v>
       </c>
       <c r="Y15" s="20" t="n">
-        <v>13690</v>
+        <v>12100</v>
       </c>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="10" t="n"/>
@@ -5850,7 +5850,7 @@
         <v>8267.299999999999</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>12495</v>
+        <v>12380</v>
       </c>
       <c r="Z18" s="11" t="n"/>
       <c r="AA18" s="10" t="n"/>
@@ -8193,11 +8193,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>13690</v>
+        <v>12100</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 11,980원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,330원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25257,7 +25257,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>103.24</v>
+        <v>91.25</v>
       </c>
     </row>
     <row r="32">
@@ -25267,7 +25267,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AJ$1</definedName>
@@ -4838,35 +4838,35 @@
         <v>1418.75</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="Z6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE6" s="11" t="n"/>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
     </row>
@@ -4942,35 +4942,35 @@
         <v>1355.4</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Z7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="11" t="n"/>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
     </row>
@@ -5046,35 +5046,35 @@
         <v>890.41</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="Z8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE8" s="11" t="n"/>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Z9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="11" t="n"/>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1631.97</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="Z10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE10" s="11" t="n"/>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
     </row>
@@ -5358,35 +5358,35 @@
         <v>1539.06</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Z11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
     </row>
@@ -5462,35 +5462,35 @@
         <v>210.43</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="Z12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE12" s="11" t="n"/>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
     </row>
@@ -5566,35 +5566,35 @@
         <v>202.16</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Z13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="11" t="n"/>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
     </row>
@@ -5681,7 +5681,7 @@
         <v>12270</v>
       </c>
       <c r="Y15" s="20" t="n">
-        <v>12100</v>
+        <v>12160</v>
       </c>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="10" t="n"/>
@@ -5897,7 +5897,7 @@
         <v>8267.299999999999</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>12380</v>
+        <v>12392</v>
       </c>
       <c r="Z18" s="11" t="n"/>
       <c r="AA18" s="10" t="n"/>
@@ -8263,11 +8263,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>12100</v>
+        <v>12160</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,330원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,720원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.01253329188933275</v>
+        <v>0.01253329188932982</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.03714067115983413</v>
+        <v>0.03714067115983267</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>73.02</v>
+        <v>73.39</v>
       </c>
     </row>
     <row r="32">
@@ -25677,7 +25677,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -4044,7 +4044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4838,35 +4838,35 @@
         <v>1418.75</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="Z6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE6" s="11" t="n"/>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
     </row>
@@ -4942,35 +4942,35 @@
         <v>1355.4</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Z7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="11" t="n"/>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
     </row>
@@ -5046,35 +5046,35 @@
         <v>890.41</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="Z8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE8" s="11" t="n"/>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Z9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="11" t="n"/>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1631.97</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="Z10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE10" s="11" t="n"/>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
     </row>
@@ -5358,35 +5358,35 @@
         <v>1539.06</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Z11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
     </row>
@@ -5462,35 +5462,35 @@
         <v>210.43</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="Z12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE12" s="11" t="n"/>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
     </row>
@@ -5566,35 +5566,35 @@
         <v>202.16</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Z13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="11" t="n"/>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -4044,7 +4044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -4044,7 +4044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
         <v>12270</v>
       </c>
       <c r="Y15" s="20" t="n">
-        <v>12160</v>
+        <v>10470</v>
       </c>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="10" t="n"/>
@@ -5825,7 +5825,7 @@
         <v>4020</v>
       </c>
       <c r="Y17" s="20" t="n">
-        <v>11520</v>
+        <v>10350</v>
       </c>
       <c r="Z17" s="11" t="n"/>
       <c r="AA17" s="10" t="n"/>
@@ -5897,7 +5897,7 @@
         <v>8267.299999999999</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>12392</v>
+        <v>12071.7</v>
       </c>
       <c r="Z18" s="11" t="n"/>
       <c r="AA18" s="10" t="n"/>
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>12160</v>
+        <v>10470</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25667,7 +25667,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>73.39</v>
+        <v>63.19</v>
       </c>
     </row>
     <row r="32">
@@ -25677,7 +25677,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -4044,7 +4044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4838,35 +4838,35 @@
         <v>1418.75</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="Z6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE6" s="11" t="n"/>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
     </row>
@@ -4942,35 +4942,35 @@
         <v>1355.4</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Z7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="11" t="n"/>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
     </row>
@@ -5046,35 +5046,35 @@
         <v>890.41</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="Z8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE8" s="11" t="n"/>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Z9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="11" t="n"/>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1631.97</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="Z10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE10" s="11" t="n"/>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
     </row>
@@ -5358,35 +5358,35 @@
         <v>1539.06</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Z11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
     </row>
@@ -5462,35 +5462,35 @@
         <v>210.43</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="Z12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE12" s="11" t="n"/>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
     </row>
@@ -5566,35 +5566,35 @@
         <v>202.16</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Z13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="11" t="n"/>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
     </row>
@@ -5681,7 +5681,7 @@
         <v>12270</v>
       </c>
       <c r="Y15" s="20" t="n">
-        <v>10470</v>
+        <v>10110</v>
       </c>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="10" t="n"/>
@@ -5825,7 +5825,7 @@
         <v>4020</v>
       </c>
       <c r="Y17" s="20" t="n">
-        <v>10350</v>
+        <v>9480</v>
       </c>
       <c r="Z17" s="11" t="n"/>
       <c r="AA17" s="10" t="n"/>
@@ -5897,7 +5897,7 @@
         <v>8267.299999999999</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>12071.7</v>
+        <v>11780</v>
       </c>
       <c r="Z18" s="11" t="n"/>
       <c r="AA18" s="10" t="n"/>
@@ -8263,11 +8263,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>10470</v>
+        <v>10110</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,720원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,170원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25667,7 +25667,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>63.19</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="32">
@@ -25677,7 +25677,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -4044,7 +4044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4838,35 +4838,35 @@
         <v>1418.75</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="Z6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE6" s="11" t="n"/>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
     </row>
@@ -4942,35 +4942,35 @@
         <v>1355.4</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Z7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="11" t="n"/>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
     </row>
@@ -5046,35 +5046,35 @@
         <v>890.41</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="Z8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE8" s="11" t="n"/>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Z9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="11" t="n"/>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1631.97</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="Z10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE10" s="11" t="n"/>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
     </row>
@@ -5358,35 +5358,35 @@
         <v>1539.06</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Z11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
     </row>
@@ -5462,35 +5462,35 @@
         <v>210.43</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="Z12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE12" s="11" t="n"/>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
     </row>
@@ -5566,35 +5566,35 @@
         <v>202.16</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Z13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="11" t="n"/>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
     </row>
@@ -5681,7 +5681,7 @@
         <v>12270</v>
       </c>
       <c r="Y15" s="20" t="n">
-        <v>10110</v>
+        <v>10590</v>
       </c>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="10" t="n"/>
@@ -5897,7 +5897,7 @@
         <v>8267.299999999999</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>11780</v>
+        <v>11618.8</v>
       </c>
       <c r="Z18" s="11" t="n"/>
       <c r="AA18" s="10" t="n"/>
@@ -8263,11 +8263,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>10110</v>
+        <v>10590</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 12,170원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,350원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25667,7 +25667,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>61.01</v>
+        <v>63.91</v>
       </c>
     </row>
     <row r="32">
@@ -25677,7 +25677,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -4044,7 +4044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4838,35 +4838,35 @@
         <v>1418.75</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="Z6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE6" s="11" t="n"/>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
     </row>
@@ -4942,35 +4942,35 @@
         <v>1355.4</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Z7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="11" t="n"/>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
     </row>
@@ -5046,35 +5046,35 @@
         <v>890.41</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="Z8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE8" s="11" t="n"/>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Z9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="11" t="n"/>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1631.97</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="Z10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE10" s="11" t="n"/>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
     </row>
@@ -5358,35 +5358,35 @@
         <v>1539.06</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Z11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
     </row>
@@ -5462,35 +5462,35 @@
         <v>210.43</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="Z12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE12" s="11" t="n"/>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
     </row>
@@ -5566,35 +5566,35 @@
         <v>202.16</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Z13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="11" t="n"/>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
     </row>
@@ -5681,7 +5681,7 @@
         <v>12270</v>
       </c>
       <c r="Y15" s="20" t="n">
-        <v>10590</v>
+        <v>10380</v>
       </c>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="10" t="n"/>
@@ -5825,7 +5825,7 @@
         <v>4020</v>
       </c>
       <c r="Y17" s="20" t="n">
-        <v>9480</v>
+        <v>9200</v>
       </c>
       <c r="Z17" s="11" t="n"/>
       <c r="AA17" s="10" t="n"/>
@@ -5897,7 +5897,7 @@
         <v>8267.299999999999</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>11618.8</v>
+        <v>11144.5</v>
       </c>
       <c r="Z18" s="11" t="n"/>
       <c r="AA18" s="10" t="n"/>
@@ -8263,11 +8263,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>10590</v>
+        <v>10380</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,350원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 9,660원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25667,7 +25667,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>63.91</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="32">
@@ -25677,7 +25677,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/012210_model.xlsx
+++ b/argus/kship/models/012210_model.xlsx
@@ -4044,7 +4044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4838,35 +4838,35 @@
         <v>1418.75</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="Z6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE6" s="11" t="n"/>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
     </row>
@@ -4942,35 +4942,35 @@
         <v>1355.4</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Z7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="11" t="n"/>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
     </row>
@@ -5046,35 +5046,35 @@
         <v>890.41</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="Z8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE8" s="11" t="n"/>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
     </row>
@@ -5150,35 +5150,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Z9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="11" t="n"/>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1631.97</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="Z10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE10" s="11" t="n"/>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
     </row>
@@ -5358,35 +5358,35 @@
         <v>1539.06</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Z11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
     </row>
@@ -5462,35 +5462,35 @@
         <v>210.43</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="Z12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE12" s="11" t="n"/>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
     </row>
@@ -5566,35 +5566,35 @@
         <v>202.16</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Z13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="11" t="n"/>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
     </row>
@@ -5681,7 +5681,7 @@
         <v>12270</v>
       </c>
       <c r="Y15" s="20" t="n">
-        <v>10380</v>
+        <v>8180</v>
       </c>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="10" t="n"/>
@@ -5825,7 +5825,7 @@
         <v>4020</v>
       </c>
       <c r="Y17" s="20" t="n">
-        <v>9200</v>
+        <v>8060</v>
       </c>
       <c r="Z17" s="11" t="n"/>
       <c r="AA17" s="10" t="n"/>
@@ -5897,7 +5897,7 @@
         <v>8267.299999999999</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>11144.5</v>
+        <v>10431.9</v>
       </c>
       <c r="Z18" s="11" t="n"/>
       <c r="AA18" s="10" t="n"/>
@@ -8263,11 +8263,11 @@
         </is>
       </c>
       <c r="D42" s="34" t="n">
-        <v>10380</v>
+        <v>8180</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 9,660원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,960원)</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19198,7 +19198,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25667,7 +25667,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>62.64</v>
+        <v>49.37</v>
       </c>
     </row>
     <row r="32">
@@ -25677,7 +25677,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.28</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="33">
